--- a/Buffer Preparation and Correction Statistic 2024-2025_rev. 0.1_2025.09.15.xlsx
+++ b/Buffer Preparation and Correction Statistic 2024-2025_rev. 0.1_2025.09.15.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.1.200\Industrial Engineering\STATISTIC\_LOT produced\L55L84L82\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\riccardo.gibertini\Desktop\Hanna Statistics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A57A280-53F8-4DC8-B00B-57ED6FB54485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5DAFCBA-EF17-4994-B609-115729BE469F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pH 1.68" sheetId="4" r:id="rId1"/>
@@ -3534,8 +3534,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Percentuale" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
@@ -3839,19 +3839,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FC98197-EA49-483C-9E4D-C1B3C28E42A9}">
   <dimension ref="A1:I22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="51.36328125" customWidth="1"/>
-    <col min="2" max="2" width="8.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="51.33203125" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.08984375" customWidth="1"/>
-    <col min="7" max="7" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.109375" customWidth="1"/>
+    <col min="7" max="7" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
         <v>3</v>
       </c>
@@ -3862,7 +3862,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="16"/>
       <c r="C2" s="16"/>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="F2" s="4"/>
     </row>
-    <row r="4" spans="1:9" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" s="1" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -3901,7 +3901,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>235</v>
       </c>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="I5" s="10"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>235</v>
       </c>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="I6" s="10"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>235</v>
       </c>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="I7" s="10"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>235</v>
       </c>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="I8" s="10"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>235</v>
       </c>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="I9" s="10"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>235</v>
       </c>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="I10" s="10"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>235</v>
       </c>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="I11" s="10"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>235</v>
       </c>
@@ -4077,7 +4077,7 @@
       </c>
       <c r="I12" s="10"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>235</v>
       </c>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="I13" s="10"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>235</v>
       </c>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="I14" s="10"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>235</v>
       </c>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="I15" s="10"/>
     </row>
-    <row r="16" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>235</v>
       </c>
@@ -4173,7 +4173,7 @@
         <v>162.4</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>235</v>
       </c>
@@ -4203,7 +4203,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>235</v>
       </c>
@@ -4233,7 +4233,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>235</v>
       </c>
@@ -4263,7 +4263,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>235</v>
       </c>
@@ -4293,7 +4293,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>235</v>
       </c>
@@ -4323,7 +4323,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>235</v>
       </c>
@@ -4360,19 +4360,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19867512-2C68-42AF-A958-3440CAF38E21}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:I179"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.81640625" customWidth="1"/>
-    <col min="2" max="2" width="8.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="50.77734375" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33.36328125" customWidth="1"/>
-    <col min="7" max="7" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.33203125" customWidth="1"/>
+    <col min="7" max="7" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
         <v>3</v>
       </c>
@@ -4386,7 +4386,7 @@
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="16"/>
       <c r="C2" s="16"/>
@@ -4399,7 +4399,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -4410,7 +4410,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:9" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" s="1" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -4439,7 +4439,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>19</v>
       </c>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="I5" s="3"/>
     </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>18</v>
       </c>
@@ -4483,7 +4483,7 @@
       </c>
       <c r="I6" s="3"/>
     </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>18</v>
       </c>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>18</v>
       </c>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="I8" s="3"/>
     </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>18</v>
       </c>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="I9" s="3"/>
     </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>18</v>
       </c>
@@ -4571,7 +4571,7 @@
       </c>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>18</v>
       </c>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="I11" s="3"/>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>19</v>
       </c>
@@ -4615,7 +4615,7 @@
       </c>
       <c r="I12" s="3"/>
     </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>19</v>
       </c>
@@ -4637,7 +4637,7 @@
       </c>
       <c r="I13" s="3"/>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>19</v>
       </c>
@@ -4659,7 +4659,7 @@
       </c>
       <c r="I14" s="3"/>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>282</v>
       </c>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="I15" s="3"/>
     </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>282</v>
       </c>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="I16" s="3"/>
     </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>18</v>
       </c>
@@ -4725,7 +4725,7 @@
       </c>
       <c r="I17" s="3"/>
     </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>18</v>
       </c>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="I18" s="3"/>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>18</v>
       </c>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="I19" s="3"/>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>18</v>
       </c>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="I20" s="3"/>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>19</v>
       </c>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="I21" s="3"/>
     </row>
-    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>19</v>
       </c>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="I22" s="3"/>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>18</v>
       </c>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="I23" s="3"/>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>18</v>
       </c>
@@ -4879,7 +4879,7 @@
       </c>
       <c r="I24" s="3"/>
     </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>18</v>
       </c>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="I25" s="3"/>
     </row>
-    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>18</v>
       </c>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="I26" s="3"/>
     </row>
-    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>18</v>
       </c>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="I27" s="3"/>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>18</v>
       </c>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="I28" s="3"/>
     </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>19</v>
       </c>
@@ -4989,7 +4989,7 @@
       </c>
       <c r="I29" s="3"/>
     </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>18</v>
       </c>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="I30" s="3"/>
     </row>
-    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
       <c r="B31" s="8" t="s">
         <v>309</v>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="I31" s="3"/>
     </row>
-    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>19</v>
       </c>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="I32" s="3"/>
     </row>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>19</v>
       </c>
@@ -5075,7 +5075,7 @@
       </c>
       <c r="I33" s="3"/>
     </row>
-    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>19</v>
       </c>
@@ -5097,7 +5097,7 @@
       </c>
       <c r="I34" s="3"/>
     </row>
-    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>19</v>
       </c>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="I35" s="3"/>
     </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>19</v>
       </c>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="I36" s="3"/>
     </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>18</v>
       </c>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="I37" s="3"/>
     </row>
-    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6"/>
       <c r="B38" s="8" t="s">
         <v>316</v>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="I38" s="3"/>
     </row>
-    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
         <v>19</v>
       </c>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="I39" s="3"/>
     </row>
-    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
         <v>18</v>
       </c>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="I40" s="3"/>
     </row>
-    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="6"/>
       <c r="B41" s="8" t="s">
         <v>319</v>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="I41" s="3"/>
     </row>
-    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
         <v>19</v>
       </c>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="I42" s="3"/>
     </row>
-    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
         <v>19</v>
       </c>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="I43" s="3"/>
     </row>
-    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>19</v>
       </c>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="I44" s="3"/>
     </row>
-    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
         <v>19</v>
       </c>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="I45" s="3"/>
     </row>
-    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>18</v>
       </c>
@@ -5365,7 +5365,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="6"/>
       <c r="B47" s="8" t="s">
         <v>324</v>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="I47" s="3"/>
     </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>18</v>
       </c>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="I48" s="3"/>
     </row>
-    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
         <v>18</v>
       </c>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="I49" s="3"/>
     </row>
-    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>18</v>
       </c>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="I50" s="3"/>
     </row>
-    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
         <v>18</v>
       </c>
@@ -5481,7 +5481,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>18</v>
       </c>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="I52" s="3"/>
     </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="6"/>
       <c r="B53" s="8" t="s">
         <v>329</v>
@@ -5523,7 +5523,7 @@
       </c>
       <c r="I53" s="3"/>
     </row>
-    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
         <v>18</v>
       </c>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="I54" s="3"/>
     </row>
-    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6"/>
       <c r="B55" s="8" t="s">
         <v>331</v>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="I55" s="3"/>
     </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
         <v>18</v>
       </c>
@@ -5595,7 +5595,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="6"/>
       <c r="B57" s="8" t="s">
         <v>22</v>
@@ -5621,7 +5621,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
         <v>18</v>
       </c>
@@ -5651,7 +5651,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="6"/>
       <c r="B59" s="8" t="s">
         <v>24</v>
@@ -5677,7 +5677,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
         <v>19</v>
       </c>
@@ -5707,7 +5707,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
         <v>18</v>
       </c>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="I61" s="3"/>
     </row>
-    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="6"/>
       <c r="B62" s="8" t="s">
         <v>333</v>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="I62" s="3"/>
     </row>
-    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
         <v>19</v>
       </c>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="I63" s="3"/>
     </row>
-    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
         <v>19</v>
       </c>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="I64" s="3"/>
     </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
         <v>18</v>
       </c>
@@ -5815,7 +5815,7 @@
       </c>
       <c r="I65" s="3"/>
     </row>
-    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="6"/>
       <c r="B66" s="8" t="s">
         <v>337</v>
@@ -5835,7 +5835,7 @@
       </c>
       <c r="I66" s="3"/>
     </row>
-    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
         <v>19</v>
       </c>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="I67" s="3"/>
     </row>
-    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
         <v>19</v>
       </c>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="I68" s="3"/>
     </row>
-    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
         <v>19</v>
       </c>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="I69" s="3"/>
     </row>
-    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
         <v>18</v>
       </c>
@@ -5923,7 +5923,7 @@
       </c>
       <c r="I70" s="3"/>
     </row>
-    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
         <v>18</v>
       </c>
@@ -5945,7 +5945,7 @@
       </c>
       <c r="I71" s="3"/>
     </row>
-    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
         <v>19</v>
       </c>
@@ -5975,7 +5975,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
         <v>19</v>
       </c>
@@ -6005,7 +6005,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
         <v>19</v>
       </c>
@@ -6035,7 +6035,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
         <v>19</v>
       </c>
@@ -6065,7 +6065,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
         <v>19</v>
       </c>
@@ -6095,7 +6095,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
         <v>18</v>
       </c>
@@ -6125,7 +6125,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="28.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="6"/>
       <c r="B78" s="8" t="s">
         <v>32</v>
@@ -6151,7 +6151,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="6" t="s">
         <v>19</v>
       </c>
@@ -6173,7 +6173,7 @@
       </c>
       <c r="I79" s="3"/>
     </row>
-    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
         <v>18</v>
       </c>
@@ -6203,7 +6203,7 @@
         <v>29.6</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" s="6"/>
       <c r="B81" s="8" t="s">
         <v>35</v>
@@ -6229,7 +6229,7 @@
         <v>29.6</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" s="6" t="s">
         <v>18</v>
       </c>
@@ -6257,7 +6257,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="6" t="s">
         <v>18</v>
       </c>
@@ -6287,7 +6287,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
         <v>18</v>
       </c>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="I84" s="3"/>
     </row>
-    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="6"/>
       <c r="B85" s="8" t="s">
         <v>345</v>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="I85" s="3"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
         <v>18</v>
       </c>
@@ -6357,7 +6357,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="6" t="s">
         <v>18</v>
       </c>
@@ -6387,7 +6387,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="6" t="s">
         <v>19</v>
       </c>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="I88" s="3"/>
     </row>
-    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
         <v>19</v>
       </c>
@@ -6439,7 +6439,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="6" t="s">
         <v>18</v>
       </c>
@@ -6469,7 +6469,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="6"/>
       <c r="B91" s="8" t="s">
         <v>347</v>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="I91" s="3"/>
     </row>
-    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="6" t="s">
         <v>19</v>
       </c>
@@ -6519,7 +6519,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="6" t="s">
         <v>19</v>
       </c>
@@ -6541,7 +6541,7 @@
       </c>
       <c r="I93" s="3"/>
     </row>
-    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="6" t="s">
         <v>19</v>
       </c>
@@ -6571,7 +6571,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="6" t="s">
         <v>19</v>
       </c>
@@ -6593,7 +6593,7 @@
       </c>
       <c r="I95" s="3"/>
     </row>
-    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="6" t="s">
         <v>18</v>
       </c>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="I96" s="3"/>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="6"/>
       <c r="B97" s="8" t="s">
         <v>351</v>
@@ -6635,7 +6635,7 @@
       </c>
       <c r="I97" s="3"/>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="6" t="s">
         <v>18</v>
       </c>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="I98" s="3"/>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="6"/>
       <c r="B99" s="8" t="s">
         <v>353</v>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="I99" s="3"/>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="6" t="s">
         <v>18</v>
       </c>
@@ -6707,7 +6707,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" s="6"/>
       <c r="B101" s="8" t="s">
         <v>45</v>
@@ -6733,7 +6733,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="6" t="s">
         <v>18</v>
       </c>
@@ -6763,7 +6763,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" s="6"/>
       <c r="B103" s="8" t="s">
         <v>47</v>
@@ -6789,7 +6789,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="6" t="s">
         <v>18</v>
       </c>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="I104" s="3"/>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="6"/>
       <c r="B105" s="8" t="s">
         <v>355</v>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="I105" s="3"/>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="6" t="s">
         <v>19</v>
       </c>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="I106" s="3"/>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="6" t="s">
         <v>19</v>
       </c>
@@ -6883,7 +6883,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="6" t="s">
         <v>19</v>
       </c>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="I108" s="3"/>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="6" t="s">
         <v>19</v>
       </c>
@@ -6935,7 +6935,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="6" t="s">
         <v>19</v>
       </c>
@@ -6965,7 +6965,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="6" t="s">
         <v>19</v>
       </c>
@@ -6995,7 +6995,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="6" t="s">
         <v>18</v>
       </c>
@@ -7017,7 +7017,7 @@
       </c>
       <c r="I112" s="3"/>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="6"/>
       <c r="B113" s="8" t="s">
         <v>359</v>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="I113" s="3"/>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="6" t="s">
         <v>19</v>
       </c>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="I114" s="3"/>
     </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="6" t="s">
         <v>19</v>
       </c>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="I115" s="3"/>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="6" t="s">
         <v>19</v>
       </c>
@@ -7111,7 +7111,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="6" t="s">
         <v>18</v>
       </c>
@@ -7141,7 +7141,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" s="6" t="s">
         <v>19</v>
       </c>
@@ -7169,7 +7169,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" s="6" t="s">
         <v>18</v>
       </c>
@@ -7197,7 +7197,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="6" t="s">
         <v>18</v>
       </c>
@@ -7227,7 +7227,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" s="6" t="s">
         <v>18</v>
       </c>
@@ -7255,7 +7255,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="6" t="s">
         <v>19</v>
       </c>
@@ -7285,7 +7285,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="6" t="s">
         <v>18</v>
       </c>
@@ -7315,7 +7315,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="6" t="s">
         <v>19</v>
       </c>
@@ -7345,7 +7345,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="6" t="s">
         <v>18</v>
       </c>
@@ -7367,7 +7367,7 @@
       </c>
       <c r="I125" s="3"/>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" s="6" t="s">
         <v>19</v>
       </c>
@@ -7397,7 +7397,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="6" t="s">
         <v>19</v>
       </c>
@@ -7419,7 +7419,7 @@
       </c>
       <c r="I127" s="3"/>
     </row>
-    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="6" t="s">
         <v>19</v>
       </c>
@@ -7441,7 +7441,7 @@
       </c>
       <c r="I128" s="3"/>
     </row>
-    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="6" t="s">
         <v>18</v>
       </c>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="I129" s="3"/>
     </row>
-    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="6" t="s">
         <v>18</v>
       </c>
@@ -7493,7 +7493,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" s="6" t="s">
         <v>18</v>
       </c>
@@ -7521,7 +7521,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="6" t="s">
         <v>18</v>
       </c>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="I132" s="3"/>
     </row>
-    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="6" t="s">
         <v>19</v>
       </c>
@@ -7573,7 +7573,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="6" t="s">
         <v>18</v>
       </c>
@@ -7603,7 +7603,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="6" t="s">
         <v>18</v>
       </c>
@@ -7625,7 +7625,7 @@
       </c>
       <c r="I135" s="3"/>
     </row>
-    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="6" t="s">
         <v>18</v>
       </c>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="I136" s="3"/>
     </row>
-    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="6" t="s">
         <v>18</v>
       </c>
@@ -7669,7 +7669,7 @@
       </c>
       <c r="I137" s="3"/>
     </row>
-    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="6" t="s">
         <v>18</v>
       </c>
@@ -7691,7 +7691,7 @@
       </c>
       <c r="I138" s="3"/>
     </row>
-    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="6" t="s">
         <v>18</v>
       </c>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="I139" s="3"/>
     </row>
-    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="6" t="s">
         <v>18</v>
       </c>
@@ -7735,7 +7735,7 @@
       </c>
       <c r="I140" s="3"/>
     </row>
-    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="6" t="s">
         <v>18</v>
       </c>
@@ -7757,7 +7757,7 @@
       </c>
       <c r="I141" s="3"/>
     </row>
-    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="6" t="s">
         <v>18</v>
       </c>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="I142" s="3"/>
     </row>
-    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="6" t="s">
         <v>18</v>
       </c>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="I143" s="3"/>
     </row>
-    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="6" t="s">
         <v>19</v>
       </c>
@@ -7823,7 +7823,7 @@
       </c>
       <c r="I144" s="3"/>
     </row>
-    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="6" t="s">
         <v>19</v>
       </c>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="I145" s="3"/>
     </row>
-    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="6" t="s">
         <v>19</v>
       </c>
@@ -7867,7 +7867,7 @@
       </c>
       <c r="I146" s="3"/>
     </row>
-    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="6" t="s">
         <v>19</v>
       </c>
@@ -7889,7 +7889,7 @@
       </c>
       <c r="I147" s="3"/>
     </row>
-    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="6" t="s">
         <v>19</v>
       </c>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="I148" s="3"/>
     </row>
-    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="6" t="s">
         <v>19</v>
       </c>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="I149" s="3"/>
     </row>
-    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="6" t="s">
         <v>19</v>
       </c>
@@ -7963,7 +7963,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="6" t="s">
         <v>18</v>
       </c>
@@ -7993,7 +7993,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="6" t="s">
         <v>19</v>
       </c>
@@ -8023,7 +8023,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="6" t="s">
         <v>18</v>
       </c>
@@ -8053,7 +8053,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="6" t="s">
         <v>18</v>
       </c>
@@ -8075,7 +8075,7 @@
       </c>
       <c r="I154" s="3"/>
     </row>
-    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="6" t="s">
         <v>19</v>
       </c>
@@ -8105,7 +8105,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="6" t="s">
         <v>19</v>
       </c>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="I156" s="3"/>
     </row>
-    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="6" t="s">
         <v>19</v>
       </c>
@@ -8149,7 +8149,7 @@
       </c>
       <c r="I157" s="3"/>
     </row>
-    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="6" t="s">
         <v>19</v>
       </c>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="I158" s="3"/>
     </row>
-    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="6" t="s">
         <v>18</v>
       </c>
@@ -8193,7 +8193,7 @@
       </c>
       <c r="I159" s="3"/>
     </row>
-    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="6" t="s">
         <v>18</v>
       </c>
@@ -8223,7 +8223,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="6" t="s">
         <v>18</v>
       </c>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="I161" s="3"/>
     </row>
-    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="6" t="s">
         <v>18</v>
       </c>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="I162" s="3"/>
     </row>
-    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="6" t="s">
         <v>18</v>
       </c>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="I163" s="3"/>
     </row>
-    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="6" t="s">
         <v>18</v>
       </c>
@@ -8311,7 +8311,7 @@
       </c>
       <c r="I164" s="3"/>
     </row>
-    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="6" t="s">
         <v>18</v>
       </c>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="I165" s="3"/>
     </row>
-    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="6" t="s">
         <v>19</v>
       </c>
@@ -8355,7 +8355,7 @@
       </c>
       <c r="I166" s="3"/>
     </row>
-    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="6" t="s">
         <v>19</v>
       </c>
@@ -8377,7 +8377,7 @@
       </c>
       <c r="I167" s="3"/>
     </row>
-    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="6" t="s">
         <v>19</v>
       </c>
@@ -8407,7 +8407,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="6" t="s">
         <v>19</v>
       </c>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="I169" s="3"/>
     </row>
-    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="6" t="s">
         <v>19</v>
       </c>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="I170" s="3"/>
     </row>
-    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="6" t="s">
         <v>19</v>
       </c>
@@ -8473,7 +8473,7 @@
       </c>
       <c r="I171" s="3"/>
     </row>
-    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="6" t="s">
         <v>19</v>
       </c>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="I172" s="3"/>
     </row>
-    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="6" t="s">
         <v>19</v>
       </c>
@@ -8525,7 +8525,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="6" t="s">
         <v>18</v>
       </c>
@@ -8547,7 +8547,7 @@
       </c>
       <c r="I174" s="3"/>
     </row>
-    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="6" t="s">
         <v>18</v>
       </c>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="I175" s="3"/>
     </row>
-    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="6" t="s">
         <v>19</v>
       </c>
@@ -8591,7 +8591,7 @@
       </c>
       <c r="I176" s="3"/>
     </row>
-    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="6" t="s">
         <v>19</v>
       </c>
@@ -8613,7 +8613,7 @@
       </c>
       <c r="I177" s="3"/>
     </row>
-    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="6" t="s">
         <v>19</v>
       </c>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="I178" s="3"/>
     </row>
-    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="6" t="s">
         <v>18</v>
       </c>
@@ -8660,7 +8660,7 @@
   </sheetData>
   <autoFilter ref="A4:I179" xr:uid="{19867512-2C68-42AF-A958-3440CAF38E21}">
     <filterColumn colId="4">
-      <colorFilter dxfId="2"/>
+      <colorFilter dxfId="1"/>
     </filterColumn>
     <filterColumn colId="5">
       <customFilters>
@@ -8680,18 +8680,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:I172"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="51.453125" customWidth="1"/>
-    <col min="3" max="3" width="12.81640625" customWidth="1"/>
+    <col min="1" max="1" width="51.44140625" customWidth="1"/>
+    <col min="3" max="3" width="12.77734375" customWidth="1"/>
     <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="34" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
         <v>3</v>
       </c>
@@ -8702,7 +8702,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="16"/>
       <c r="C2" s="16"/>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="F2" s="4"/>
     </row>
-    <row r="4" spans="1:9" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" s="1" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -8741,7 +8741,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>85</v>
       </c>
@@ -8763,7 +8763,7 @@
       </c>
       <c r="I5" s="3"/>
     </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>85</v>
       </c>
@@ -8785,7 +8785,7 @@
       </c>
       <c r="I6" s="3"/>
     </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>85</v>
       </c>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>85</v>
       </c>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="I8" s="3"/>
     </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>85</v>
       </c>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="I9" s="3"/>
     </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>85</v>
       </c>
@@ -8873,7 +8873,7 @@
       </c>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>86</v>
       </c>
@@ -8895,7 +8895,7 @@
       </c>
       <c r="I11" s="3"/>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>86</v>
       </c>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="I12" s="3"/>
     </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>86</v>
       </c>
@@ -8939,7 +8939,7 @@
       </c>
       <c r="I13" s="3"/>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>84</v>
       </c>
@@ -8961,7 +8961,7 @@
       </c>
       <c r="I14" s="3"/>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>84</v>
       </c>
@@ -8983,7 +8983,7 @@
       </c>
       <c r="I15" s="3"/>
     </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>84</v>
       </c>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="I16" s="3"/>
     </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>84</v>
       </c>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="I17" s="3"/>
     </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>85</v>
       </c>
@@ -9049,7 +9049,7 @@
       </c>
       <c r="I18" s="3"/>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>85</v>
       </c>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="I19" s="3"/>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>86</v>
       </c>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="I20" s="3"/>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>86</v>
       </c>
@@ -9115,7 +9115,7 @@
       </c>
       <c r="I21" s="3"/>
     </row>
-    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>86</v>
       </c>
@@ -9137,7 +9137,7 @@
       </c>
       <c r="I22" s="3"/>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>84</v>
       </c>
@@ -9159,7 +9159,7 @@
       </c>
       <c r="I23" s="3"/>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>84</v>
       </c>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="I24" s="3"/>
     </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>86</v>
       </c>
@@ -9203,7 +9203,7 @@
       </c>
       <c r="I25" s="3"/>
     </row>
-    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>86</v>
       </c>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="I26" s="3"/>
     </row>
-    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>86</v>
       </c>
@@ -9247,7 +9247,7 @@
       </c>
       <c r="I27" s="3"/>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>85</v>
       </c>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="I28" s="3"/>
     </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>85</v>
       </c>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="I29" s="3"/>
     </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>86</v>
       </c>
@@ -9313,7 +9313,7 @@
       </c>
       <c r="I30" s="3"/>
     </row>
-    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>84</v>
       </c>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="I31" s="3"/>
     </row>
-    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6"/>
       <c r="B32" s="8" t="s">
         <v>574</v>
@@ -9355,7 +9355,7 @@
       </c>
       <c r="I32" s="3"/>
     </row>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>86</v>
       </c>
@@ -9377,7 +9377,7 @@
       </c>
       <c r="I33" s="3"/>
     </row>
-    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>86</v>
       </c>
@@ -9399,7 +9399,7 @@
       </c>
       <c r="I34" s="3"/>
     </row>
-    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>84</v>
       </c>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="I35" s="3"/>
     </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6"/>
       <c r="B36" s="8" t="s">
         <v>578</v>
@@ -9441,7 +9441,7 @@
       </c>
       <c r="I36" s="3"/>
     </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>86</v>
       </c>
@@ -9463,7 +9463,7 @@
       </c>
       <c r="I37" s="3"/>
     </row>
-    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>86</v>
       </c>
@@ -9485,7 +9485,7 @@
       </c>
       <c r="I38" s="3"/>
     </row>
-    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
         <v>86</v>
       </c>
@@ -9507,7 +9507,7 @@
       </c>
       <c r="I39" s="3"/>
     </row>
-    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
         <v>86</v>
       </c>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="I40" s="3"/>
     </row>
-    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
         <v>86</v>
       </c>
@@ -9551,7 +9551,7 @@
       </c>
       <c r="I41" s="3"/>
     </row>
-    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
         <v>85</v>
       </c>
@@ -9573,7 +9573,7 @@
       </c>
       <c r="I42" s="3"/>
     </row>
-    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="6"/>
       <c r="B43" s="8" t="s">
         <v>585</v>
@@ -9593,7 +9593,7 @@
       </c>
       <c r="I43" s="3"/>
     </row>
-    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>85</v>
       </c>
@@ -9615,7 +9615,7 @@
       </c>
       <c r="I44" s="3"/>
     </row>
-    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="6"/>
       <c r="B45" s="8" t="s">
         <v>587</v>
@@ -9635,7 +9635,7 @@
       </c>
       <c r="I45" s="3"/>
     </row>
-    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>86</v>
       </c>
@@ -9657,7 +9657,7 @@
       </c>
       <c r="I46" s="3"/>
     </row>
-    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
         <v>84</v>
       </c>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="I47" s="3"/>
     </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6"/>
       <c r="B48" s="8" t="s">
         <v>590</v>
@@ -9699,7 +9699,7 @@
       </c>
       <c r="I48" s="3"/>
     </row>
-    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
         <v>86</v>
       </c>
@@ -9721,7 +9721,7 @@
       </c>
       <c r="I49" s="3"/>
     </row>
-    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>86</v>
       </c>
@@ -9743,7 +9743,7 @@
       </c>
       <c r="I50" s="3"/>
     </row>
-    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
         <v>86</v>
       </c>
@@ -9765,7 +9765,7 @@
       </c>
       <c r="I51" s="3"/>
     </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>86</v>
       </c>
@@ -9787,7 +9787,7 @@
       </c>
       <c r="I52" s="3"/>
     </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
         <v>83</v>
       </c>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="I53" s="3"/>
     </row>
-    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
         <v>83</v>
       </c>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="I54" s="3"/>
     </row>
-    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>83</v>
       </c>
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I55" s="3"/>
     </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
         <v>83</v>
       </c>
@@ -9883,7 +9883,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
         <v>84</v>
       </c>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="I57" s="3"/>
     </row>
-    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
         <v>84</v>
       </c>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="I58" s="3"/>
     </row>
-    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
         <v>83</v>
       </c>
@@ -9957,7 +9957,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
         <v>83</v>
       </c>
@@ -9987,7 +9987,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
         <v>84</v>
       </c>
@@ -10017,7 +10017,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="6"/>
       <c r="B62" s="8" t="s">
         <v>91</v>
@@ -10043,7 +10043,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
         <v>84</v>
       </c>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="I63" s="3"/>
     </row>
-    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="6"/>
       <c r="B64" s="8" t="s">
         <v>601</v>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="I64" s="3"/>
     </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
         <v>84</v>
       </c>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="I65" s="3"/>
     </row>
-    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
         <v>84</v>
       </c>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="I66" s="3"/>
     </row>
-    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
         <v>84</v>
       </c>
@@ -10159,7 +10159,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="6"/>
       <c r="B68" s="8" t="s">
         <v>93</v>
@@ -10185,7 +10185,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
         <v>83</v>
       </c>
@@ -10207,7 +10207,7 @@
       </c>
       <c r="I69" s="3"/>
     </row>
-    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
         <v>83</v>
       </c>
@@ -10237,7 +10237,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
         <v>84</v>
       </c>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="I71" s="3"/>
     </row>
-    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
         <v>84</v>
       </c>
@@ -10281,7 +10281,7 @@
       </c>
       <c r="I72" s="3"/>
     </row>
-    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
         <v>83</v>
       </c>
@@ -10311,7 +10311,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
         <v>83</v>
       </c>
@@ -10333,7 +10333,7 @@
       </c>
       <c r="I74" s="3"/>
     </row>
-    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
         <v>83</v>
       </c>
@@ -10363,7 +10363,7 @@
         <v>70.900000000000006</v>
       </c>
     </row>
-    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
         <v>83</v>
       </c>
@@ -10385,7 +10385,7 @@
       </c>
       <c r="I76" s="3"/>
     </row>
-    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
         <v>85</v>
       </c>
@@ -10415,7 +10415,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="6"/>
       <c r="B78" s="8" t="s">
         <v>98</v>
@@ -10441,7 +10441,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="6" t="s">
         <v>86</v>
       </c>
@@ -10471,7 +10471,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
         <v>86</v>
       </c>
@@ -10493,7 +10493,7 @@
       </c>
       <c r="I80" s="3"/>
     </row>
-    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="6" t="s">
         <v>86</v>
       </c>
@@ -10523,7 +10523,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="6" t="s">
         <v>86</v>
       </c>
@@ -10545,7 +10545,7 @@
       </c>
       <c r="I82" s="3"/>
     </row>
-    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="6" t="s">
         <v>86</v>
       </c>
@@ -10567,7 +10567,7 @@
       </c>
       <c r="I83" s="3"/>
     </row>
-    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
         <v>86</v>
       </c>
@@ -10589,7 +10589,7 @@
       </c>
       <c r="I84" s="3"/>
     </row>
-    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="6" t="s">
         <v>85</v>
       </c>
@@ -10611,7 +10611,7 @@
       </c>
       <c r="I85" s="3"/>
     </row>
-    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="6"/>
       <c r="B86" s="8" t="s">
         <v>614</v>
@@ -10631,7 +10631,7 @@
       </c>
       <c r="I86" s="3"/>
     </row>
-    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="6" t="s">
         <v>85</v>
       </c>
@@ -10653,7 +10653,7 @@
       </c>
       <c r="I87" s="3"/>
     </row>
-    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="6"/>
       <c r="B88" s="8" t="s">
         <v>616</v>
@@ -10673,7 +10673,7 @@
       </c>
       <c r="I88" s="3"/>
     </row>
-    <row r="89" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
         <v>86</v>
       </c>
@@ -10703,7 +10703,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="6" t="s">
         <v>85</v>
       </c>
@@ -10725,7 +10725,7 @@
       </c>
       <c r="I90" s="3"/>
     </row>
-    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="6"/>
       <c r="B91" s="8" t="s">
         <v>618</v>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="I91" s="3"/>
     </row>
-    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="6" t="s">
         <v>86</v>
       </c>
@@ -10767,7 +10767,7 @@
       </c>
       <c r="I92" s="3"/>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" s="6" t="s">
         <v>85</v>
       </c>
@@ -10797,7 +10797,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" s="6"/>
       <c r="B94" s="8" t="s">
         <v>103</v>
@@ -10823,7 +10823,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="6" t="s">
         <v>546</v>
       </c>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="I95" s="3"/>
     </row>
-    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="6" t="s">
         <v>86</v>
       </c>
@@ -10867,7 +10867,7 @@
       </c>
       <c r="I96" s="3"/>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="6" t="s">
         <v>86</v>
       </c>
@@ -10889,7 +10889,7 @@
       </c>
       <c r="I97" s="3"/>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="6" t="s">
         <v>85</v>
       </c>
@@ -10919,7 +10919,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" s="6"/>
       <c r="B99" s="8" t="s">
         <v>105</v>
@@ -10945,7 +10945,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="6" t="s">
         <v>86</v>
       </c>
@@ -10975,7 +10975,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="6" t="s">
         <v>86</v>
       </c>
@@ -11005,7 +11005,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="6" t="s">
         <v>86</v>
       </c>
@@ -11035,7 +11035,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="6" t="s">
         <v>86</v>
       </c>
@@ -11057,7 +11057,7 @@
       </c>
       <c r="I103" s="3"/>
     </row>
-    <row r="104" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="6" t="s">
         <v>86</v>
       </c>
@@ -11079,7 +11079,7 @@
       </c>
       <c r="I104" s="3"/>
     </row>
-    <row r="105" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="6" t="s">
         <v>86</v>
       </c>
@@ -11101,7 +11101,7 @@
       </c>
       <c r="I105" s="3"/>
     </row>
-    <row r="106" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="6" t="s">
         <v>85</v>
       </c>
@@ -11123,7 +11123,7 @@
       </c>
       <c r="I106" s="3"/>
     </row>
-    <row r="107" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="6" t="s">
         <v>85</v>
       </c>
@@ -11145,7 +11145,7 @@
       </c>
       <c r="I107" s="3"/>
     </row>
-    <row r="108" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="6" t="s">
         <v>85</v>
       </c>
@@ -11167,7 +11167,7 @@
       </c>
       <c r="I108" s="3"/>
     </row>
-    <row r="109" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="6" t="s">
         <v>85</v>
       </c>
@@ -11189,7 +11189,7 @@
       </c>
       <c r="I109" s="3"/>
     </row>
-    <row r="110" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="6" t="s">
         <v>85</v>
       </c>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="I110" s="3"/>
     </row>
-    <row r="111" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="6" t="s">
         <v>85</v>
       </c>
@@ -11233,7 +11233,7 @@
       </c>
       <c r="I111" s="3"/>
     </row>
-    <row r="112" spans="1:9" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="6" t="s">
         <v>86</v>
       </c>
@@ -11261,7 +11261,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="6" t="s">
         <v>85</v>
       </c>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="I113" s="3"/>
     </row>
-    <row r="114" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="6" t="s">
         <v>86</v>
       </c>
@@ -11313,7 +11313,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="6" t="s">
         <v>85</v>
       </c>
@@ -11335,7 +11335,7 @@
       </c>
       <c r="I115" s="3"/>
     </row>
-    <row r="116" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="6" t="s">
         <v>86</v>
       </c>
@@ -11357,7 +11357,7 @@
       </c>
       <c r="I116" s="3"/>
     </row>
-    <row r="117" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="6" t="s">
         <v>86</v>
       </c>
@@ -11379,7 +11379,7 @@
       </c>
       <c r="I117" s="3"/>
     </row>
-    <row r="118" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="6" t="s">
         <v>86</v>
       </c>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="I118" s="3"/>
     </row>
-    <row r="119" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="6" t="s">
         <v>86</v>
       </c>
@@ -11423,7 +11423,7 @@
       </c>
       <c r="I119" s="3"/>
     </row>
-    <row r="120" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="6" t="s">
         <v>85</v>
       </c>
@@ -11445,7 +11445,7 @@
       </c>
       <c r="I120" s="3"/>
     </row>
-    <row r="121" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="6" t="s">
         <v>85</v>
       </c>
@@ -11475,7 +11475,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="6" t="s">
         <v>85</v>
       </c>
@@ -11505,7 +11505,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="6" t="s">
         <v>85</v>
       </c>
@@ -11527,7 +11527,7 @@
       </c>
       <c r="I123" s="3"/>
     </row>
-    <row r="124" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="6" t="s">
         <v>85</v>
       </c>
@@ -11549,7 +11549,7 @@
       </c>
       <c r="I124" s="3"/>
     </row>
-    <row r="125" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="6" t="s">
         <v>86</v>
       </c>
@@ -11579,7 +11579,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="6" t="s">
         <v>86</v>
       </c>
@@ -11601,7 +11601,7 @@
       </c>
       <c r="I126" s="3"/>
     </row>
-    <row r="127" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="6" t="s">
         <v>86</v>
       </c>
@@ -11623,7 +11623,7 @@
       </c>
       <c r="I127" s="3"/>
     </row>
-    <row r="128" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="6" t="s">
         <v>85</v>
       </c>
@@ -11645,7 +11645,7 @@
       </c>
       <c r="I128" s="3"/>
     </row>
-    <row r="129" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="6" t="s">
         <v>86</v>
       </c>
@@ -11675,7 +11675,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="6" t="s">
         <v>85</v>
       </c>
@@ -11697,7 +11697,7 @@
       </c>
       <c r="I130" s="3"/>
     </row>
-    <row r="131" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="6" t="s">
         <v>85</v>
       </c>
@@ -11719,7 +11719,7 @@
       </c>
       <c r="I131" s="3"/>
     </row>
-    <row r="132" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="6" t="s">
         <v>85</v>
       </c>
@@ -11741,7 +11741,7 @@
       </c>
       <c r="I132" s="3"/>
     </row>
-    <row r="133" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="6" t="s">
         <v>85</v>
       </c>
@@ -11763,7 +11763,7 @@
       </c>
       <c r="I133" s="3"/>
     </row>
-    <row r="134" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="6" t="s">
         <v>85</v>
       </c>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="I134" s="3"/>
     </row>
-    <row r="135" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="6" t="s">
         <v>86</v>
       </c>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="I135" s="3"/>
     </row>
-    <row r="136" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="6" t="s">
         <v>85</v>
       </c>
@@ -11837,7 +11837,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="6" t="s">
         <v>85</v>
       </c>
@@ -11859,7 +11859,7 @@
       </c>
       <c r="I137" s="3"/>
     </row>
-    <row r="138" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="6" t="s">
         <v>85</v>
       </c>
@@ -11881,7 +11881,7 @@
       </c>
       <c r="I138" s="3"/>
     </row>
-    <row r="139" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="6" t="s">
         <v>85</v>
       </c>
@@ -11911,7 +11911,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="6" t="s">
         <v>86</v>
       </c>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="I140" s="3"/>
     </row>
-    <row r="141" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="6" t="s">
         <v>85</v>
       </c>
@@ -11955,7 +11955,7 @@
       </c>
       <c r="I141" s="3"/>
     </row>
-    <row r="142" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="6" t="s">
         <v>86</v>
       </c>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="I142" s="3"/>
     </row>
-    <row r="143" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="6" t="s">
         <v>85</v>
       </c>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="I143" s="3"/>
     </row>
-    <row r="144" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="6" t="s">
         <v>85</v>
       </c>
@@ -12021,7 +12021,7 @@
       </c>
       <c r="I144" s="3"/>
     </row>
-    <row r="145" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="6" t="s">
         <v>85</v>
       </c>
@@ -12043,7 +12043,7 @@
       </c>
       <c r="I145" s="3"/>
     </row>
-    <row r="146" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="6" t="s">
         <v>85</v>
       </c>
@@ -12065,7 +12065,7 @@
       </c>
       <c r="I146" s="3"/>
     </row>
-    <row r="147" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="6" t="s">
         <v>86</v>
       </c>
@@ -12087,7 +12087,7 @@
       </c>
       <c r="I147" s="3"/>
     </row>
-    <row r="148" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="6" t="s">
         <v>86</v>
       </c>
@@ -12109,7 +12109,7 @@
       </c>
       <c r="I148" s="3"/>
     </row>
-    <row r="149" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="6" t="s">
         <v>86</v>
       </c>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="I149" s="3"/>
     </row>
-    <row r="150" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="6" t="s">
         <v>86</v>
       </c>
@@ -12153,7 +12153,7 @@
       </c>
       <c r="I150" s="3"/>
     </row>
-    <row r="151" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="6" t="s">
         <v>86</v>
       </c>
@@ -12175,7 +12175,7 @@
       </c>
       <c r="I151" s="3"/>
     </row>
-    <row r="152" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="6" t="s">
         <v>86</v>
       </c>
@@ -12197,7 +12197,7 @@
       </c>
       <c r="I152" s="3"/>
     </row>
-    <row r="153" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="6" t="s">
         <v>86</v>
       </c>
@@ -12219,7 +12219,7 @@
       </c>
       <c r="I153" s="3"/>
     </row>
-    <row r="154" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="6" t="s">
         <v>85</v>
       </c>
@@ -12241,7 +12241,7 @@
       </c>
       <c r="I154" s="3"/>
     </row>
-    <row r="155" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="6" t="s">
         <v>85</v>
       </c>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="I155" s="3"/>
     </row>
-    <row r="156" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="6" t="s">
         <v>85</v>
       </c>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="I156" s="3"/>
     </row>
-    <row r="157" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="6" t="s">
         <v>85</v>
       </c>
@@ -12307,7 +12307,7 @@
       </c>
       <c r="I157" s="3"/>
     </row>
-    <row r="158" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="6" t="s">
         <v>85</v>
       </c>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="I158" s="3"/>
     </row>
-    <row r="159" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="6" t="s">
         <v>85</v>
       </c>
@@ -12351,7 +12351,7 @@
       </c>
       <c r="I159" s="3"/>
     </row>
-    <row r="160" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="6" t="s">
         <v>86</v>
       </c>
@@ -12373,7 +12373,7 @@
       </c>
       <c r="I160" s="3"/>
     </row>
-    <row r="161" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="6" t="s">
         <v>86</v>
       </c>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="I161" s="3"/>
     </row>
-    <row r="162" spans="1:9" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="6" t="s">
         <v>86</v>
       </c>
@@ -12425,7 +12425,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="6" t="s">
         <v>86</v>
       </c>
@@ -12455,7 +12455,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="164" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="6" t="s">
         <v>86</v>
       </c>
@@ -12477,7 +12477,7 @@
       </c>
       <c r="I164" s="3"/>
     </row>
-    <row r="165" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="6" t="s">
         <v>86</v>
       </c>
@@ -12499,7 +12499,7 @@
       </c>
       <c r="I165" s="3"/>
     </row>
-    <row r="166" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="6" t="s">
         <v>85</v>
       </c>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="I166" s="3"/>
     </row>
-    <row r="167" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="6" t="s">
         <v>85</v>
       </c>
@@ -12543,7 +12543,7 @@
       </c>
       <c r="I167" s="3"/>
     </row>
-    <row r="168" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="6" t="s">
         <v>86</v>
       </c>
@@ -12565,7 +12565,7 @@
       </c>
       <c r="I168" s="3"/>
     </row>
-    <row r="169" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="6" t="s">
         <v>86</v>
       </c>
@@ -12587,7 +12587,7 @@
       </c>
       <c r="I169" s="3"/>
     </row>
-    <row r="170" spans="1:9" s="4" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:9" s="4" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="6" t="s">
         <v>86</v>
       </c>
@@ -12617,7 +12617,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="6" t="s">
         <v>86</v>
       </c>
@@ -12639,7 +12639,7 @@
       </c>
       <c r="I171" s="3"/>
     </row>
-    <row r="172" spans="1:9" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:9" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="6" t="s">
         <v>86</v>
       </c>
@@ -12664,7 +12664,7 @@
   </sheetData>
   <autoFilter ref="A4:I172" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="4">
-      <colorFilter dxfId="1"/>
+      <colorFilter dxfId="0"/>
     </filterColumn>
     <filterColumn colId="5">
       <customFilters>
@@ -12684,19 +12684,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A44E2E99-673F-4C5C-98E6-22FF6EADC8CD}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:I92"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="51.36328125" customWidth="1"/>
-    <col min="2" max="2" width="8.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="51.33203125" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="20.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
         <v>3</v>
       </c>
@@ -12707,7 +12707,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="16"/>
       <c r="C2" s="16"/>
@@ -12717,7 +12717,7 @@
       </c>
       <c r="F2" s="4"/>
     </row>
-    <row r="4" spans="1:9" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" s="1" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -12746,7 +12746,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>150</v>
       </c>
@@ -12774,7 +12774,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>151</v>
       </c>
@@ -12796,7 +12796,7 @@
       </c>
       <c r="I6" s="10"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>151</v>
       </c>
@@ -12824,7 +12824,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>151</v>
       </c>
@@ -12846,7 +12846,7 @@
       </c>
       <c r="I8" s="10"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>151</v>
       </c>
@@ -12874,7 +12874,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>150</v>
       </c>
@@ -12896,7 +12896,7 @@
       </c>
       <c r="I10" s="10"/>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>150</v>
       </c>
@@ -12918,7 +12918,7 @@
       </c>
       <c r="I11" s="10"/>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>151</v>
       </c>
@@ -12940,7 +12940,7 @@
       </c>
       <c r="I12" s="10"/>
     </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>151</v>
       </c>
@@ -12962,7 +12962,7 @@
       </c>
       <c r="I13" s="10"/>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>150</v>
       </c>
@@ -12992,7 +12992,7 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>150</v>
       </c>
@@ -13022,7 +13022,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>151</v>
       </c>
@@ -13044,7 +13044,7 @@
       </c>
       <c r="I16" s="10"/>
     </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6"/>
       <c r="B17" s="8" t="s">
         <v>823</v>
@@ -13064,7 +13064,7 @@
       </c>
       <c r="I17" s="10"/>
     </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>150</v>
       </c>
@@ -13086,7 +13086,7 @@
       </c>
       <c r="I18" s="10"/>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>150</v>
       </c>
@@ -13108,7 +13108,7 @@
       </c>
       <c r="I19" s="10"/>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>150</v>
       </c>
@@ -13130,7 +13130,7 @@
       </c>
       <c r="I20" s="10"/>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>151</v>
       </c>
@@ -13160,7 +13160,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="6"/>
       <c r="B22" s="8" t="s">
         <v>158</v>
@@ -13186,7 +13186,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>151</v>
       </c>
@@ -13208,7 +13208,7 @@
       </c>
       <c r="I23" s="10"/>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6"/>
       <c r="B24" s="8" t="s">
         <v>828</v>
@@ -13228,7 +13228,7 @@
       </c>
       <c r="I24" s="10"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>150</v>
       </c>
@@ -13258,7 +13258,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>151</v>
       </c>
@@ -13288,7 +13288,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="6"/>
       <c r="B27" s="8" t="s">
         <v>161</v>
@@ -13314,7 +13314,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>150</v>
       </c>
@@ -13344,7 +13344,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>151</v>
       </c>
@@ -13366,7 +13366,7 @@
       </c>
       <c r="I29" s="10"/>
     </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6"/>
       <c r="B30" s="8" t="s">
         <v>830</v>
@@ -13386,7 +13386,7 @@
       </c>
       <c r="I30" s="10"/>
     </row>
-    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>150</v>
       </c>
@@ -13408,7 +13408,7 @@
       </c>
       <c r="I31" s="10"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>150</v>
       </c>
@@ -13438,7 +13438,7 @@
         <v>37.200000000000003</v>
       </c>
     </row>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>150</v>
       </c>
@@ -13468,7 +13468,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>150</v>
       </c>
@@ -13498,7 +13498,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>151</v>
       </c>
@@ -13528,7 +13528,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="6"/>
       <c r="B36" s="8" t="s">
         <v>167</v>
@@ -13554,7 +13554,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>151</v>
       </c>
@@ -13582,7 +13582,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>151</v>
       </c>
@@ -13612,7 +13612,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
         <v>151</v>
       </c>
@@ -13642,7 +13642,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="6"/>
       <c r="B40" s="8" t="s">
         <v>171</v>
@@ -13668,7 +13668,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
         <v>150</v>
       </c>
@@ -13690,7 +13690,7 @@
       </c>
       <c r="I41" s="10"/>
     </row>
-    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
         <v>151</v>
       </c>
@@ -13712,7 +13712,7 @@
       </c>
       <c r="I42" s="10"/>
     </row>
-    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="6"/>
       <c r="B43" s="8" t="s">
         <v>834</v>
@@ -13732,7 +13732,7 @@
       </c>
       <c r="I43" s="10"/>
     </row>
-    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>150</v>
       </c>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="I44" s="10"/>
     </row>
-    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
         <v>151</v>
       </c>
@@ -13784,7 +13784,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="6"/>
       <c r="B46" s="8" t="s">
         <v>173</v>
@@ -13810,7 +13810,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
         <v>150</v>
       </c>
@@ -13840,7 +13840,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>150</v>
       </c>
@@ -13862,7 +13862,7 @@
       </c>
       <c r="I48" s="10"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
         <v>150</v>
       </c>
@@ -13892,7 +13892,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>151</v>
       </c>
@@ -13914,7 +13914,7 @@
       </c>
       <c r="I50" s="10"/>
     </row>
-    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="6"/>
       <c r="B51" s="8" t="s">
         <v>838</v>
@@ -13934,7 +13934,7 @@
       </c>
       <c r="I51" s="10"/>
     </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>150</v>
       </c>
@@ -13956,7 +13956,7 @@
       </c>
       <c r="I52" s="10"/>
     </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
         <v>151</v>
       </c>
@@ -13978,7 +13978,7 @@
       </c>
       <c r="I53" s="10"/>
     </row>
-    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="6"/>
       <c r="B54" s="8" t="s">
         <v>841</v>
@@ -13998,7 +13998,7 @@
       </c>
       <c r="I54" s="10"/>
     </row>
-    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>150</v>
       </c>
@@ -14028,7 +14028,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
         <v>150</v>
       </c>
@@ -14058,7 +14058,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
         <v>150</v>
       </c>
@@ -14080,7 +14080,7 @@
       </c>
       <c r="I57" s="10"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="22" t="s">
         <v>150</v>
       </c>
@@ -14110,7 +14110,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
         <v>150</v>
       </c>
@@ -14140,7 +14140,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
         <v>151</v>
       </c>
@@ -14170,7 +14170,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
         <v>150</v>
       </c>
@@ -14200,7 +14200,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
         <v>151</v>
       </c>
@@ -14228,7 +14228,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
         <v>150</v>
       </c>
@@ -14258,7 +14258,7 @@
         <v>90.1</v>
       </c>
     </row>
-    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
         <v>150</v>
       </c>
@@ -14280,7 +14280,7 @@
       </c>
       <c r="I64" s="10"/>
     </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
         <v>150</v>
       </c>
@@ -14302,7 +14302,7 @@
       </c>
       <c r="I65" s="10"/>
     </row>
-    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
         <v>150</v>
       </c>
@@ -14332,7 +14332,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
         <v>151</v>
       </c>
@@ -14362,7 +14362,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
         <v>151</v>
       </c>
@@ -14392,7 +14392,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
         <v>151</v>
       </c>
@@ -14414,7 +14414,7 @@
       </c>
       <c r="I69" s="10"/>
     </row>
-    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
         <v>150</v>
       </c>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="I70" s="10"/>
     </row>
-    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
         <v>150</v>
       </c>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="I71" s="10"/>
     </row>
-    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
         <v>150</v>
       </c>
@@ -14480,7 +14480,7 @@
       </c>
       <c r="I72" s="10"/>
     </row>
-    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
         <v>150</v>
       </c>
@@ -14502,7 +14502,7 @@
       </c>
       <c r="I73" s="10"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
         <v>151</v>
       </c>
@@ -14532,7 +14532,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
         <v>150</v>
       </c>
@@ -14554,7 +14554,7 @@
       </c>
       <c r="I75" s="10"/>
     </row>
-    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
         <v>150</v>
       </c>
@@ -14576,7 +14576,7 @@
       </c>
       <c r="I76" s="10"/>
     </row>
-    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
         <v>150</v>
       </c>
@@ -14598,7 +14598,7 @@
       </c>
       <c r="I77" s="10"/>
     </row>
-    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
         <v>151</v>
       </c>
@@ -14620,7 +14620,7 @@
       </c>
       <c r="I78" s="10"/>
     </row>
-    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="6" t="s">
         <v>150</v>
       </c>
@@ -14650,7 +14650,7 @@
         <v>11.3222</v>
       </c>
     </row>
-    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
         <v>151</v>
       </c>
@@ -14680,7 +14680,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="6" t="s">
         <v>150</v>
       </c>
@@ -14702,7 +14702,7 @@
       </c>
       <c r="I81" s="10"/>
     </row>
-    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="6" t="s">
         <v>150</v>
       </c>
@@ -14732,7 +14732,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="6" t="s">
         <v>150</v>
       </c>
@@ -14762,7 +14762,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
         <v>150</v>
       </c>
@@ -14792,7 +14792,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="6" t="s">
         <v>150</v>
       </c>
@@ -14822,7 +14822,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
         <v>151</v>
       </c>
@@ -14852,7 +14852,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="6" t="s">
         <v>151</v>
       </c>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="I87" s="10"/>
     </row>
-    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="6" t="s">
         <v>151</v>
       </c>
@@ -14896,7 +14896,7 @@
       </c>
       <c r="I88" s="10"/>
     </row>
-    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
         <v>150</v>
       </c>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="I89" s="10"/>
     </row>
-    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="6" t="s">
         <v>150</v>
       </c>
@@ -14940,7 +14940,7 @@
       </c>
       <c r="I90" s="10"/>
     </row>
-    <row r="91" spans="1:9" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
         <v>150</v>
       </c>
@@ -14970,7 +14970,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="6" t="s">
         <v>150</v>
       </c>
@@ -14995,7 +14995,7 @@
   </sheetData>
   <autoFilter ref="A4:I92" xr:uid="{A44E2E99-673F-4C5C-98E6-22FF6EADC8CD}">
     <filterColumn colId="4">
-      <colorFilter dxfId="0"/>
+      <colorFilter dxfId="2"/>
     </filterColumn>
     <filterColumn colId="5">
       <customFilters>
@@ -15014,16 +15014,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{280714C8-97D1-4A89-B57B-50D729D43762}">
   <dimension ref="A2:E10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.6328125" customWidth="1"/>
-    <col min="2" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.6328125" customWidth="1"/>
-    <col min="4" max="4" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>1098</v>
       </c>
@@ -15040,7 +15040,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="13">
         <v>1</v>
       </c>
@@ -15057,7 +15057,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="13">
         <v>2</v>
       </c>
@@ -15074,7 +15074,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="13">
         <v>3</v>
       </c>
@@ -15091,7 +15091,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="13">
         <v>4</v>
       </c>
@@ -15108,7 +15108,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="13">
         <v>5</v>
       </c>
@@ -15125,7 +15125,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="13">
         <v>6</v>
       </c>
@@ -15142,7 +15142,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="13">
         <v>7</v>
       </c>
@@ -15159,7 +15159,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="13">
         <v>8</v>
       </c>
